--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432064</v>
+        <v>124432066</v>
       </c>
       <c r="B7" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,25 +1282,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341317</v>
+        <v>341335</v>
       </c>
       <c r="R7" t="n">
-        <v>6504715</v>
+        <v>6504703</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432068</v>
+        <v>124432062</v>
       </c>
       <c r="B8" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,38 +1384,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341322</v>
+        <v>341309</v>
       </c>
       <c r="R8" t="n">
-        <v>6504653</v>
+        <v>6504714</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,6 +1463,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1474,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432062</v>
+        <v>124432067</v>
       </c>
       <c r="B9" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,39 +1510,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341309</v>
+        <v>341328</v>
       </c>
       <c r="R9" t="n">
-        <v>6504714</v>
+        <v>6504682</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1565,21 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432066</v>
+        <v>124432068</v>
       </c>
       <c r="B10" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341335</v>
+        <v>341322</v>
       </c>
       <c r="R10" t="n">
-        <v>6504703</v>
+        <v>6504653</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432059</v>
+        <v>124432060</v>
       </c>
       <c r="B11" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1710,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341336</v>
+        <v>341333</v>
       </c>
       <c r="R11" t="n">
-        <v>6504747</v>
+        <v>6504740</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432067</v>
+        <v>124432064</v>
       </c>
       <c r="B12" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341328</v>
+        <v>341317</v>
       </c>
       <c r="R12" t="n">
-        <v>6504682</v>
+        <v>6504715</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432063</v>
+        <v>124432065</v>
       </c>
       <c r="B13" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,31 +1918,36 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341315</v>
+        <v>341325</v>
       </c>
       <c r="R13" t="n">
         <v>6504707</v>
@@ -1988,6 +1993,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2004,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432060</v>
+        <v>124432059</v>
       </c>
       <c r="B14" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2044,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341333</v>
+        <v>341336</v>
       </c>
       <c r="R14" t="n">
-        <v>6504740</v>
+        <v>6504747</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2106,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432065</v>
+        <v>124432063</v>
       </c>
       <c r="B15" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2122,36 +2142,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341325</v>
+        <v>341315</v>
       </c>
       <c r="R15" t="n">
         <v>6504707</v>
@@ -2197,21 +2212,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432066</v>
+        <v>124432061</v>
       </c>
       <c r="B7" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,34 +1286,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341335</v>
+        <v>341321</v>
       </c>
       <c r="R7" t="n">
-        <v>6504703</v>
+        <v>6504727</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,6 +1361,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1372,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432062</v>
+        <v>124432066</v>
       </c>
       <c r="B8" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341309</v>
+        <v>341335</v>
       </c>
       <c r="R8" t="n">
-        <v>6504714</v>
+        <v>6504703</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1463,21 +1478,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432068</v>
+        <v>124432062</v>
       </c>
       <c r="B10" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1608,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341322</v>
+        <v>341309</v>
       </c>
       <c r="R10" t="n">
-        <v>6504653</v>
+        <v>6504714</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,6 +1687,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1800,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432064</v>
+        <v>124432059</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,25 +1832,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341317</v>
+        <v>341336</v>
       </c>
       <c r="R12" t="n">
-        <v>6504715</v>
+        <v>6504747</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2024,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432059</v>
+        <v>124432063</v>
       </c>
       <c r="B14" t="n">
         <v>95089</v>
@@ -2064,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341336</v>
+        <v>341315</v>
       </c>
       <c r="R14" t="n">
-        <v>6504747</v>
+        <v>6504707</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432063</v>
+        <v>124432064</v>
       </c>
       <c r="B15" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,25 +2158,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341315</v>
+        <v>341317</v>
       </c>
       <c r="R15" t="n">
-        <v>6504707</v>
+        <v>6504715</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432061</v>
+        <v>124432068</v>
       </c>
       <c r="B16" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,43 +2260,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341321</v>
+        <v>341322</v>
       </c>
       <c r="R16" t="n">
-        <v>6504727</v>
+        <v>6504653</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2319,21 +2334,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432061</v>
+        <v>124432063</v>
       </c>
       <c r="B7" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341321</v>
+        <v>341315</v>
       </c>
       <c r="R7" t="n">
-        <v>6504727</v>
+        <v>6504707</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1361,21 +1356,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1392,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432066</v>
+        <v>124432059</v>
       </c>
       <c r="B8" t="n">
         <v>95089</v>
@@ -1432,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341335</v>
+        <v>341336</v>
       </c>
       <c r="R8" t="n">
-        <v>6504703</v>
+        <v>6504747</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1494,7 +1474,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432067</v>
+        <v>124432066</v>
       </c>
       <c r="B9" t="n">
         <v>95089</v>
@@ -1534,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341328</v>
+        <v>341335</v>
       </c>
       <c r="R9" t="n">
-        <v>6504682</v>
+        <v>6504703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1596,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432062</v>
+        <v>124432064</v>
       </c>
       <c r="B10" t="n">
-        <v>8361</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,43 +1588,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341309</v>
+        <v>341317</v>
       </c>
       <c r="R10" t="n">
-        <v>6504714</v>
+        <v>6504715</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1687,21 +1662,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432060</v>
+        <v>124432065</v>
       </c>
       <c r="B11" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,38 +1690,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341333</v>
+        <v>341325</v>
       </c>
       <c r="R11" t="n">
-        <v>6504740</v>
+        <v>6504707</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1804,6 +1769,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1820,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432059</v>
+        <v>124432062</v>
       </c>
       <c r="B12" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,34 +1816,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341336</v>
+        <v>341309</v>
       </c>
       <c r="R12" t="n">
-        <v>6504747</v>
+        <v>6504714</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1906,6 +1891,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432065</v>
+        <v>124432067</v>
       </c>
       <c r="B13" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,39 +1938,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341325</v>
+        <v>341328</v>
       </c>
       <c r="R13" t="n">
-        <v>6504707</v>
+        <v>6504682</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2013,21 +2008,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2044,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432063</v>
+        <v>124432068</v>
       </c>
       <c r="B14" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341315</v>
+        <v>341322</v>
       </c>
       <c r="R14" t="n">
-        <v>6504707</v>
+        <v>6504653</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2146,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432064</v>
+        <v>124432060</v>
       </c>
       <c r="B15" t="n">
-        <v>100279</v>
+        <v>96729</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2142,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341317</v>
+        <v>341333</v>
       </c>
       <c r="R15" t="n">
-        <v>6504715</v>
+        <v>6504740</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432068</v>
+        <v>124432061</v>
       </c>
       <c r="B16" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,38 +2240,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341322</v>
+        <v>341321</v>
       </c>
       <c r="R16" t="n">
-        <v>6504653</v>
+        <v>6504727</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2334,6 +2319,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432063</v>
+        <v>124432065</v>
       </c>
       <c r="B7" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,31 +1286,36 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341315</v>
+        <v>341325</v>
       </c>
       <c r="R7" t="n">
         <v>6504707</v>
@@ -1356,6 +1361,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1372,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432059</v>
+        <v>124432061</v>
       </c>
       <c r="B8" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,34 +1408,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341336</v>
+        <v>341321</v>
       </c>
       <c r="R8" t="n">
-        <v>6504747</v>
+        <v>6504727</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1458,6 +1483,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1474,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432066</v>
+        <v>124432064</v>
       </c>
       <c r="B9" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1526,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1554,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341335</v>
+        <v>341317</v>
       </c>
       <c r="R9" t="n">
-        <v>6504703</v>
+        <v>6504715</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432064</v>
+        <v>124432067</v>
       </c>
       <c r="B10" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,25 +1628,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1656,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341317</v>
+        <v>341328</v>
       </c>
       <c r="R10" t="n">
-        <v>6504715</v>
+        <v>6504682</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1678,7 +1718,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432065</v>
+        <v>124432062</v>
       </c>
       <c r="B11" t="n">
         <v>8361</v>
@@ -1723,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341325</v>
+        <v>341309</v>
       </c>
       <c r="R11" t="n">
-        <v>6504707</v>
+        <v>6504714</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432062</v>
+        <v>124432059</v>
       </c>
       <c r="B12" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,39 +1856,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341309</v>
+        <v>341336</v>
       </c>
       <c r="R12" t="n">
-        <v>6504714</v>
+        <v>6504747</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1891,21 +1926,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1922,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432067</v>
+        <v>124432060</v>
       </c>
       <c r="B13" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,25 +1954,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341328</v>
+        <v>341333</v>
       </c>
       <c r="R13" t="n">
-        <v>6504682</v>
+        <v>6504740</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2024,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432068</v>
+        <v>124432063</v>
       </c>
       <c r="B14" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2056,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341322</v>
+        <v>341315</v>
       </c>
       <c r="R14" t="n">
-        <v>6504653</v>
+        <v>6504707</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432060</v>
+        <v>124432066</v>
       </c>
       <c r="B15" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,25 +2158,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341333</v>
+        <v>341335</v>
       </c>
       <c r="R15" t="n">
-        <v>6504740</v>
+        <v>6504703</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432061</v>
+        <v>124432068</v>
       </c>
       <c r="B16" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,43 +2260,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341321</v>
+        <v>341322</v>
       </c>
       <c r="R16" t="n">
-        <v>6504727</v>
+        <v>6504653</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2319,21 +2334,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432067</v>
+        <v>124432062</v>
       </c>
       <c r="B10" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,34 +1632,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341328</v>
+        <v>341309</v>
       </c>
       <c r="R10" t="n">
-        <v>6504682</v>
+        <v>6504714</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1702,6 +1707,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1738,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432062</v>
+        <v>124432067</v>
       </c>
       <c r="B11" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,39 +1754,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341309</v>
+        <v>341328</v>
       </c>
       <c r="R11" t="n">
-        <v>6504714</v>
+        <v>6504682</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1809,21 +1824,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432065</v>
+        <v>124432061</v>
       </c>
       <c r="B7" t="n">
         <v>8361</v>
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341325</v>
+        <v>341321</v>
       </c>
       <c r="R7" t="n">
-        <v>6504707</v>
+        <v>6504727</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1392,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432061</v>
+        <v>124432065</v>
       </c>
       <c r="B8" t="n">
         <v>8361</v>
@@ -1437,10 +1437,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341321</v>
+        <v>341325</v>
       </c>
       <c r="R8" t="n">
-        <v>6504727</v>
+        <v>6504707</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1514,10 +1514,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432064</v>
+        <v>124432066</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1526,25 +1526,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341317</v>
+        <v>341335</v>
       </c>
       <c r="R9" t="n">
-        <v>6504715</v>
+        <v>6504703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432062</v>
+        <v>124432059</v>
       </c>
       <c r="B10" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,39 +1632,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341309</v>
+        <v>341336</v>
       </c>
       <c r="R10" t="n">
-        <v>6504714</v>
+        <v>6504747</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1707,21 +1702,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1738,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432067</v>
+        <v>124432060</v>
       </c>
       <c r="B11" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1750,25 +1730,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1778,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341328</v>
+        <v>341333</v>
       </c>
       <c r="R11" t="n">
-        <v>6504682</v>
+        <v>6504740</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1840,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432059</v>
+        <v>124432068</v>
       </c>
       <c r="B12" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,25 +1832,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1860,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341336</v>
+        <v>341322</v>
       </c>
       <c r="R12" t="n">
-        <v>6504747</v>
+        <v>6504653</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1942,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432060</v>
+        <v>124432064</v>
       </c>
       <c r="B13" t="n">
-        <v>96729</v>
+        <v>100279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341333</v>
+        <v>341317</v>
       </c>
       <c r="R13" t="n">
-        <v>6504740</v>
+        <v>6504715</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2146,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432066</v>
+        <v>124432062</v>
       </c>
       <c r="B15" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,34 +2142,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341335</v>
+        <v>341309</v>
       </c>
       <c r="R15" t="n">
-        <v>6504703</v>
+        <v>6504714</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2232,6 +2217,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432068</v>
+        <v>124432067</v>
       </c>
       <c r="B16" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341322</v>
+        <v>341328</v>
       </c>
       <c r="R16" t="n">
-        <v>6504653</v>
+        <v>6504682</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1392,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432065</v>
+        <v>124432066</v>
       </c>
       <c r="B8" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,39 +1408,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341325</v>
+        <v>341335</v>
       </c>
       <c r="R8" t="n">
-        <v>6504707</v>
+        <v>6504703</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1483,21 +1478,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1514,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432066</v>
+        <v>124432059</v>
       </c>
       <c r="B9" t="n">
         <v>95089</v>
@@ -1554,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341335</v>
+        <v>341336</v>
       </c>
       <c r="R9" t="n">
-        <v>6504703</v>
+        <v>6504747</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1616,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432059</v>
+        <v>124432068</v>
       </c>
       <c r="B10" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1656,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341336</v>
+        <v>341322</v>
       </c>
       <c r="R10" t="n">
-        <v>6504747</v>
+        <v>6504653</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1718,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432060</v>
+        <v>124432062</v>
       </c>
       <c r="B11" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,38 +1710,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341333</v>
+        <v>341309</v>
       </c>
       <c r="R11" t="n">
-        <v>6504740</v>
+        <v>6504714</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1804,6 +1789,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1820,10 +1820,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432068</v>
+        <v>124432065</v>
       </c>
       <c r="B12" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,38 +1832,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341322</v>
+        <v>341325</v>
       </c>
       <c r="R12" t="n">
-        <v>6504653</v>
+        <v>6504707</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1906,6 +1911,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1922,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432064</v>
+        <v>124432060</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
+        <v>96729</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1958,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341317</v>
+        <v>341333</v>
       </c>
       <c r="R13" t="n">
-        <v>6504715</v>
+        <v>6504740</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2024,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432063</v>
+        <v>124432067</v>
       </c>
       <c r="B14" t="n">
         <v>95089</v>
@@ -2064,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341315</v>
+        <v>341328</v>
       </c>
       <c r="R14" t="n">
-        <v>6504707</v>
+        <v>6504682</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432062</v>
+        <v>124432063</v>
       </c>
       <c r="B15" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,39 +2162,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341309</v>
+        <v>341315</v>
       </c>
       <c r="R15" t="n">
-        <v>6504714</v>
+        <v>6504707</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2217,21 +2232,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432067</v>
+        <v>124432064</v>
       </c>
       <c r="B16" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341328</v>
+        <v>341317</v>
       </c>
       <c r="R16" t="n">
-        <v>6504682</v>
+        <v>6504715</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432061</v>
+        <v>124432066</v>
       </c>
       <c r="B7" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341321</v>
+        <v>341335</v>
       </c>
       <c r="R7" t="n">
-        <v>6504727</v>
+        <v>6504703</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1361,21 +1356,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1392,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432066</v>
+        <v>124432060</v>
       </c>
       <c r="B8" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,25 +1384,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1432,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341335</v>
+        <v>341333</v>
       </c>
       <c r="R8" t="n">
-        <v>6504703</v>
+        <v>6504740</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1494,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432059</v>
+        <v>124432065</v>
       </c>
       <c r="B9" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,34 +1490,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341336</v>
+        <v>341325</v>
       </c>
       <c r="R9" t="n">
-        <v>6504747</v>
+        <v>6504707</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1580,6 +1565,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432068</v>
+        <v>124432061</v>
       </c>
       <c r="B10" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1608,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341322</v>
+        <v>341321</v>
       </c>
       <c r="R10" t="n">
-        <v>6504653</v>
+        <v>6504727</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,6 +1687,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1820,10 +1840,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432065</v>
+        <v>124432063</v>
       </c>
       <c r="B12" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,36 +1856,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341325</v>
+        <v>341315</v>
       </c>
       <c r="R12" t="n">
         <v>6504707</v>
@@ -1911,21 +1926,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1942,10 +1942,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432060</v>
+        <v>124432064</v>
       </c>
       <c r="B13" t="n">
-        <v>96729</v>
+        <v>100279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,21 +1958,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1982,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341333</v>
+        <v>341317</v>
       </c>
       <c r="R13" t="n">
-        <v>6504740</v>
+        <v>6504715</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432067</v>
+        <v>124432059</v>
       </c>
       <c r="B14" t="n">
         <v>95089</v>
@@ -2084,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341328</v>
+        <v>341336</v>
       </c>
       <c r="R14" t="n">
-        <v>6504682</v>
+        <v>6504747</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432063</v>
+        <v>124432068</v>
       </c>
       <c r="B15" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,25 +2158,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341315</v>
+        <v>341322</v>
       </c>
       <c r="R15" t="n">
-        <v>6504707</v>
+        <v>6504653</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432064</v>
+        <v>124432067</v>
       </c>
       <c r="B16" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341317</v>
+        <v>341328</v>
       </c>
       <c r="R16" t="n">
-        <v>6504715</v>
+        <v>6504682</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432066</v>
+        <v>124432065</v>
       </c>
       <c r="B7" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,34 +1286,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341335</v>
+        <v>341325</v>
       </c>
       <c r="R7" t="n">
-        <v>6504703</v>
+        <v>6504707</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,6 +1361,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1372,10 +1392,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432060</v>
+        <v>124432067</v>
       </c>
       <c r="B8" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,25 +1404,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341333</v>
+        <v>341328</v>
       </c>
       <c r="R8" t="n">
-        <v>6504740</v>
+        <v>6504682</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432065</v>
+        <v>124432068</v>
       </c>
       <c r="B9" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,43 +1506,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341325</v>
+        <v>341322</v>
       </c>
       <c r="R9" t="n">
-        <v>6504707</v>
+        <v>6504653</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1565,21 +1580,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432061</v>
+        <v>124432060</v>
       </c>
       <c r="B10" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,43 +1608,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341321</v>
+        <v>341333</v>
       </c>
       <c r="R10" t="n">
-        <v>6504727</v>
+        <v>6504740</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1687,21 +1682,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432062</v>
+        <v>124432063</v>
       </c>
       <c r="B11" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,39 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341309</v>
+        <v>341315</v>
       </c>
       <c r="R11" t="n">
-        <v>6504714</v>
+        <v>6504707</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1809,21 +1784,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1840,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432063</v>
+        <v>124432064</v>
       </c>
       <c r="B12" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1852,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1880,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341315</v>
+        <v>341317</v>
       </c>
       <c r="R12" t="n">
-        <v>6504707</v>
+        <v>6504715</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1942,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432064</v>
+        <v>124432061</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
+        <v>8361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,38 +1914,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341317</v>
+        <v>341321</v>
       </c>
       <c r="R13" t="n">
-        <v>6504715</v>
+        <v>6504727</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2028,6 +1993,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2044,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432059</v>
+        <v>124432062</v>
       </c>
       <c r="B14" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,34 +2040,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341336</v>
+        <v>341309</v>
       </c>
       <c r="R14" t="n">
-        <v>6504747</v>
+        <v>6504714</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2130,6 +2115,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2146,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432068</v>
+        <v>124432059</v>
       </c>
       <c r="B15" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,25 +2158,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341322</v>
+        <v>341336</v>
       </c>
       <c r="R15" t="n">
-        <v>6504653</v>
+        <v>6504747</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432067</v>
+        <v>124432066</v>
       </c>
       <c r="B16" t="n">
         <v>95089</v>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341328</v>
+        <v>341335</v>
       </c>
       <c r="R16" t="n">
-        <v>6504682</v>
+        <v>6504703</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432065</v>
+        <v>124432060</v>
       </c>
       <c r="B7" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,43 +1282,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341325</v>
+        <v>341333</v>
       </c>
       <c r="R7" t="n">
-        <v>6504707</v>
+        <v>6504740</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1361,21 +1356,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1392,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432067</v>
+        <v>124432066</v>
       </c>
       <c r="B8" t="n">
         <v>95089</v>
@@ -1432,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341328</v>
+        <v>341335</v>
       </c>
       <c r="R8" t="n">
-        <v>6504682</v>
+        <v>6504703</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1494,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432068</v>
+        <v>124432063</v>
       </c>
       <c r="B9" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341322</v>
+        <v>341315</v>
       </c>
       <c r="R9" t="n">
-        <v>6504653</v>
+        <v>6504707</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1596,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432060</v>
+        <v>124432062</v>
       </c>
       <c r="B10" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1588,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341333</v>
+        <v>341309</v>
       </c>
       <c r="R10" t="n">
-        <v>6504740</v>
+        <v>6504714</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,6 +1667,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432063</v>
+        <v>124432064</v>
       </c>
       <c r="B11" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1710,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341315</v>
+        <v>341317</v>
       </c>
       <c r="R11" t="n">
-        <v>6504707</v>
+        <v>6504715</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432064</v>
+        <v>124432065</v>
       </c>
       <c r="B12" t="n">
-        <v>100279</v>
+        <v>8361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,38 +1812,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341317</v>
+        <v>341325</v>
       </c>
       <c r="R12" t="n">
-        <v>6504715</v>
+        <v>6504707</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,6 +1891,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1902,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432061</v>
+        <v>124432068</v>
       </c>
       <c r="B13" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,43 +1934,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341321</v>
+        <v>341322</v>
       </c>
       <c r="R13" t="n">
-        <v>6504727</v>
+        <v>6504653</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1993,21 +2008,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432062</v>
+        <v>124432059</v>
       </c>
       <c r="B14" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,39 +2040,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341309</v>
+        <v>341336</v>
       </c>
       <c r="R14" t="n">
-        <v>6504714</v>
+        <v>6504747</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2115,21 +2110,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2146,7 +2126,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432059</v>
+        <v>124432067</v>
       </c>
       <c r="B15" t="n">
         <v>95089</v>
@@ -2186,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341336</v>
+        <v>341328</v>
       </c>
       <c r="R15" t="n">
-        <v>6504747</v>
+        <v>6504682</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432066</v>
+        <v>124432061</v>
       </c>
       <c r="B16" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,34 +2244,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341335</v>
+        <v>341321</v>
       </c>
       <c r="R16" t="n">
-        <v>6504703</v>
+        <v>6504727</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2334,6 +2319,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432060</v>
+        <v>124432061</v>
       </c>
       <c r="B7" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,38 +1282,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341333</v>
+        <v>341321</v>
       </c>
       <c r="R7" t="n">
-        <v>6504740</v>
+        <v>6504727</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1356,6 +1361,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1372,7 +1392,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432066</v>
+        <v>124432067</v>
       </c>
       <c r="B8" t="n">
         <v>95089</v>
@@ -1412,10 +1432,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341335</v>
+        <v>341328</v>
       </c>
       <c r="R8" t="n">
-        <v>6504703</v>
+        <v>6504682</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432063</v>
+        <v>124432064</v>
       </c>
       <c r="B9" t="n">
-        <v>95089</v>
+        <v>100279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1506,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>782</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341315</v>
+        <v>341317</v>
       </c>
       <c r="R9" t="n">
-        <v>6504707</v>
+        <v>6504715</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432062</v>
+        <v>124432060</v>
       </c>
       <c r="B10" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,43 +1608,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341309</v>
+        <v>341333</v>
       </c>
       <c r="R10" t="n">
-        <v>6504714</v>
+        <v>6504740</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,21 +1682,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432064</v>
+        <v>124432063</v>
       </c>
       <c r="B11" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1710,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341317</v>
+        <v>341315</v>
       </c>
       <c r="R11" t="n">
-        <v>6504715</v>
+        <v>6504707</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432065</v>
+        <v>124432059</v>
       </c>
       <c r="B12" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,39 +1816,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341325</v>
+        <v>341336</v>
       </c>
       <c r="R12" t="n">
-        <v>6504707</v>
+        <v>6504747</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1891,21 +1886,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1922,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432068</v>
+        <v>124432065</v>
       </c>
       <c r="B13" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,38 +1914,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341322</v>
+        <v>341325</v>
       </c>
       <c r="R13" t="n">
-        <v>6504653</v>
+        <v>6504707</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2008,6 +1993,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,7 +2024,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432059</v>
+        <v>124432066</v>
       </c>
       <c r="B14" t="n">
         <v>95089</v>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341336</v>
+        <v>341335</v>
       </c>
       <c r="R14" t="n">
-        <v>6504747</v>
+        <v>6504703</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432067</v>
+        <v>124432068</v>
       </c>
       <c r="B15" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,25 +2138,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341328</v>
+        <v>341322</v>
       </c>
       <c r="R15" t="n">
-        <v>6504682</v>
+        <v>6504653</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432061</v>
+        <v>124432062</v>
       </c>
       <c r="B16" t="n">
         <v>8361</v>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341321</v>
+        <v>341309</v>
       </c>
       <c r="R16" t="n">
-        <v>6504727</v>
+        <v>6504714</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432061</v>
+        <v>124432066</v>
       </c>
       <c r="B7" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,39 +1286,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341321</v>
+        <v>341335</v>
       </c>
       <c r="R7" t="n">
-        <v>6504727</v>
+        <v>6504703</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1361,21 +1356,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1392,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432067</v>
+        <v>124432061</v>
       </c>
       <c r="B8" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,34 +1388,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341328</v>
+        <v>341321</v>
       </c>
       <c r="R8" t="n">
-        <v>6504682</v>
+        <v>6504727</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1478,6 +1463,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1596,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432060</v>
+        <v>124432059</v>
       </c>
       <c r="B10" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,25 +1608,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341333</v>
+        <v>341336</v>
       </c>
       <c r="R10" t="n">
-        <v>6504740</v>
+        <v>6504747</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432063</v>
+        <v>124432060</v>
       </c>
       <c r="B11" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1710,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341315</v>
+        <v>341333</v>
       </c>
       <c r="R11" t="n">
-        <v>6504707</v>
+        <v>6504740</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432059</v>
+        <v>124432067</v>
       </c>
       <c r="B12" t="n">
         <v>95089</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341336</v>
+        <v>341328</v>
       </c>
       <c r="R12" t="n">
-        <v>6504747</v>
+        <v>6504682</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432065</v>
+        <v>124432063</v>
       </c>
       <c r="B13" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,36 +1918,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341325</v>
+        <v>341315</v>
       </c>
       <c r="R13" t="n">
         <v>6504707</v>
@@ -1993,21 +1988,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2024,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432066</v>
+        <v>124432062</v>
       </c>
       <c r="B14" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,34 +2020,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341335</v>
+        <v>341309</v>
       </c>
       <c r="R14" t="n">
-        <v>6504703</v>
+        <v>6504714</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2110,6 +2095,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432068</v>
+        <v>124432065</v>
       </c>
       <c r="B15" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,38 +2138,43 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341322</v>
+        <v>341325</v>
       </c>
       <c r="R15" t="n">
-        <v>6504653</v>
+        <v>6504707</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2212,6 +2217,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2228,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432062</v>
+        <v>124432068</v>
       </c>
       <c r="B16" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2240,43 +2260,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341309</v>
+        <v>341322</v>
       </c>
       <c r="R16" t="n">
-        <v>6504714</v>
+        <v>6504653</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2319,21 +2334,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432061</v>
+        <v>124432064</v>
       </c>
       <c r="B8" t="n">
-        <v>8361</v>
+        <v>100279</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,43 +1384,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341321</v>
+        <v>341317</v>
       </c>
       <c r="R8" t="n">
-        <v>6504727</v>
+        <v>6504715</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1463,21 +1458,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432064</v>
+        <v>124432068</v>
       </c>
       <c r="B9" t="n">
-        <v>100279</v>
+        <v>96729</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341317</v>
+        <v>341322</v>
       </c>
       <c r="R9" t="n">
-        <v>6504715</v>
+        <v>6504653</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1596,7 +1576,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432059</v>
+        <v>124432067</v>
       </c>
       <c r="B10" t="n">
         <v>95089</v>
@@ -1636,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341336</v>
+        <v>341328</v>
       </c>
       <c r="R10" t="n">
-        <v>6504747</v>
+        <v>6504682</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1698,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432060</v>
+        <v>124432059</v>
       </c>
       <c r="B11" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1690,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341333</v>
+        <v>341336</v>
       </c>
       <c r="R11" t="n">
-        <v>6504740</v>
+        <v>6504747</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,7 +1780,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432067</v>
+        <v>124432063</v>
       </c>
       <c r="B12" t="n">
         <v>95089</v>
@@ -1840,10 +1820,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341328</v>
+        <v>341315</v>
       </c>
       <c r="R12" t="n">
-        <v>6504682</v>
+        <v>6504707</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1902,10 +1882,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432063</v>
+        <v>124432062</v>
       </c>
       <c r="B13" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1918,34 +1898,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341315</v>
+        <v>341309</v>
       </c>
       <c r="R13" t="n">
-        <v>6504707</v>
+        <v>6504714</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1988,6 +1973,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2004,7 +2004,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432062</v>
+        <v>124432065</v>
       </c>
       <c r="B14" t="n">
         <v>8361</v>
@@ -2049,10 +2049,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341309</v>
+        <v>341325</v>
       </c>
       <c r="R14" t="n">
-        <v>6504714</v>
+        <v>6504707</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432065</v>
+        <v>124432061</v>
       </c>
       <c r="B15" t="n">
         <v>8361</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341325</v>
+        <v>341321</v>
       </c>
       <c r="R15" t="n">
-        <v>6504707</v>
+        <v>6504727</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,7 +2248,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432068</v>
+        <v>124432060</v>
       </c>
       <c r="B16" t="n">
         <v>96729</v>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341322</v>
+        <v>341333</v>
       </c>
       <c r="R16" t="n">
-        <v>6504653</v>
+        <v>6504740</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432066</v>
+        <v>124432063</v>
       </c>
       <c r="B7" t="n">
         <v>95089</v>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341335</v>
+        <v>341315</v>
       </c>
       <c r="R7" t="n">
-        <v>6504703</v>
+        <v>6504707</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432064</v>
+        <v>124432067</v>
       </c>
       <c r="B8" t="n">
-        <v>100279</v>
+        <v>95089</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,25 +1384,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>782</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341317</v>
+        <v>341328</v>
       </c>
       <c r="R8" t="n">
-        <v>6504715</v>
+        <v>6504682</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432068</v>
+        <v>124432059</v>
       </c>
       <c r="B9" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341322</v>
+        <v>341336</v>
       </c>
       <c r="R9" t="n">
-        <v>6504653</v>
+        <v>6504747</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432067</v>
+        <v>124432061</v>
       </c>
       <c r="B10" t="n">
-        <v>95089</v>
+        <v>8361</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,34 +1592,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>782</v>
+        <v>106540</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341328</v>
+        <v>341321</v>
       </c>
       <c r="R10" t="n">
-        <v>6504682</v>
+        <v>6504727</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1662,6 +1667,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1678,7 +1698,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432059</v>
+        <v>124432066</v>
       </c>
       <c r="B11" t="n">
         <v>95089</v>
@@ -1718,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341336</v>
+        <v>341335</v>
       </c>
       <c r="R11" t="n">
-        <v>6504747</v>
+        <v>6504703</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1780,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432063</v>
+        <v>124432060</v>
       </c>
       <c r="B12" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1792,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1820,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341315</v>
+        <v>341333</v>
       </c>
       <c r="R12" t="n">
-        <v>6504707</v>
+        <v>6504740</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1882,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432062</v>
+        <v>124432064</v>
       </c>
       <c r="B13" t="n">
-        <v>8361</v>
+        <v>100279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,43 +1914,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341309</v>
+        <v>341317</v>
       </c>
       <c r="R13" t="n">
-        <v>6504714</v>
+        <v>6504715</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1973,21 +1988,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432061</v>
+        <v>124432068</v>
       </c>
       <c r="B15" t="n">
-        <v>8361</v>
+        <v>96729</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,43 +2138,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106540</v>
+        <v>2569</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341321</v>
+        <v>341322</v>
       </c>
       <c r="R15" t="n">
-        <v>6504727</v>
+        <v>6504653</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2217,21 +2212,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2248,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432060</v>
+        <v>124432062</v>
       </c>
       <c r="B16" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2260,38 +2240,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341333</v>
+        <v>341309</v>
       </c>
       <c r="R16" t="n">
-        <v>6504740</v>
+        <v>6504714</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2334,6 +2319,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 32397-2021 artfynd.xlsx
+++ b/artfynd/A 32397-2021 artfynd.xlsx
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124432063</v>
+        <v>124432066</v>
       </c>
       <c r="B7" t="n">
         <v>95089</v>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>341315</v>
+        <v>341335</v>
       </c>
       <c r="R7" t="n">
-        <v>6504707</v>
+        <v>6504703</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124432067</v>
+        <v>124432068</v>
       </c>
       <c r="B8" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1384,25 +1384,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>341328</v>
+        <v>341322</v>
       </c>
       <c r="R8" t="n">
-        <v>6504682</v>
+        <v>6504653</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124432059</v>
+        <v>124432060</v>
       </c>
       <c r="B9" t="n">
-        <v>95089</v>
+        <v>96729</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,25 +1486,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>782</v>
+        <v>2569</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skirmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hookeria lucens</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Sm.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>341336</v>
+        <v>341333</v>
       </c>
       <c r="R9" t="n">
-        <v>6504747</v>
+        <v>6504740</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124432061</v>
+        <v>124432064</v>
       </c>
       <c r="B10" t="n">
-        <v>8361</v>
+        <v>100279</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,43 +1588,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106540</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>341321</v>
+        <v>341317</v>
       </c>
       <c r="R10" t="n">
-        <v>6504727</v>
+        <v>6504715</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1667,21 +1662,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1698,7 +1678,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124432066</v>
+        <v>124432067</v>
       </c>
       <c r="B11" t="n">
         <v>95089</v>
@@ -1738,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>341335</v>
+        <v>341328</v>
       </c>
       <c r="R11" t="n">
-        <v>6504703</v>
+        <v>6504682</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1800,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124432060</v>
+        <v>124432061</v>
       </c>
       <c r="B12" t="n">
-        <v>96729</v>
+        <v>8361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,38 +1792,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2569</v>
+        <v>106540</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>341333</v>
+        <v>341321</v>
       </c>
       <c r="R12" t="n">
-        <v>6504740</v>
+        <v>6504727</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,6 +1871,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124432064</v>
+        <v>124432062</v>
       </c>
       <c r="B13" t="n">
-        <v>100279</v>
+        <v>8361</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1914,38 +1914,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>106540</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>341317</v>
+        <v>341309</v>
       </c>
       <c r="R13" t="n">
-        <v>6504715</v>
+        <v>6504714</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1988,6 +1993,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2004,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124432065</v>
+        <v>124432059</v>
       </c>
       <c r="B14" t="n">
-        <v>8361</v>
+        <v>95089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2020,39 +2040,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106540</v>
+        <v>782</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Drågebäcken, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>341325</v>
+        <v>341336</v>
       </c>
       <c r="R14" t="n">
-        <v>6504707</v>
+        <v>6504747</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2095,21 +2110,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124432068</v>
+        <v>124432063</v>
       </c>
       <c r="B15" t="n">
-        <v>96729</v>
+        <v>95089</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2138,25 +2138,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2569</v>
+        <v>782</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Skirmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Hookeria lucens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Sm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>341322</v>
+        <v>341315</v>
       </c>
       <c r="R15" t="n">
-        <v>6504653</v>
+        <v>6504707</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124432062</v>
+        <v>124432065</v>
       </c>
       <c r="B16" t="n">
         <v>8361</v>
@@ -2273,10 +2273,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>341309</v>
+        <v>341325</v>
       </c>
       <c r="R16" t="n">
-        <v>6504714</v>
+        <v>6504707</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
